--- a/Team-Data/2014-15/1-24-2014-15.xlsx
+++ b/Team-Data/2014-15/1-24-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>7.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -751,7 +818,7 @@
         <v>2</v>
       </c>
       <c r="AH2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI2" t="n">
         <v>12</v>
@@ -778,7 +845,7 @@
         <v>18</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR2" t="n">
         <v>29</v>
@@ -787,7 +854,7 @@
         <v>12</v>
       </c>
       <c r="AT2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU2" t="n">
         <v>2</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-24-2014-15</t>
+          <t>2015-01-24</t>
         </is>
       </c>
     </row>
@@ -924,10 +991,10 @@
         <v>29</v>
       </c>
       <c r="AE3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG3" t="n">
         <v>23</v>
@@ -960,34 +1027,34 @@
         <v>27</v>
       </c>
       <c r="AQ3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS3" t="n">
         <v>13</v>
       </c>
       <c r="AT3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU3" t="n">
         <v>3</v>
       </c>
       <c r="AV3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW3" t="n">
         <v>10</v>
       </c>
       <c r="AX3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA3" t="n">
         <v>30</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-24-2014-15</t>
+          <t>2015-01-24</t>
         </is>
       </c>
     </row>
@@ -1025,97 +1092,97 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E4" t="n">
         <v>18</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G4" t="n">
-        <v>0.409</v>
+        <v>0.419</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
       </c>
       <c r="I4" t="n">
-        <v>36</v>
+        <v>36.1</v>
       </c>
       <c r="J4" t="n">
-        <v>81.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="K4" t="n">
-        <v>0.444</v>
+        <v>0.445</v>
       </c>
       <c r="L4" t="n">
         <v>6.6</v>
       </c>
       <c r="M4" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="N4" t="n">
         <v>0.317</v>
       </c>
       <c r="O4" t="n">
-        <v>16.4</v>
+        <v>16.6</v>
       </c>
       <c r="P4" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.747</v>
+        <v>0.749</v>
       </c>
       <c r="R4" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>32.1</v>
+        <v>32.3</v>
       </c>
       <c r="T4" t="n">
-        <v>41.8</v>
+        <v>42.1</v>
       </c>
       <c r="U4" t="n">
         <v>20.5</v>
       </c>
       <c r="V4" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="W4" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X4" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="Y4" t="n">
         <v>4.7</v>
       </c>
       <c r="Z4" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>95</v>
+        <v>95.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>-3.7</v>
+        <v>-3</v>
       </c>
       <c r="AD4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH4" t="n">
         <v>8</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>19</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>9</v>
       </c>
       <c r="AI4" t="n">
         <v>24</v>
@@ -1130,7 +1197,7 @@
         <v>24</v>
       </c>
       <c r="AM4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AN4" t="n">
         <v>28</v>
@@ -1148,22 +1215,22 @@
         <v>26</v>
       </c>
       <c r="AS4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AT4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AU4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AV4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AW4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AX4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AY4" t="n">
         <v>11</v>
@@ -1178,7 +1245,7 @@
         <v>25</v>
       </c>
       <c r="BC4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-24-2014-15</t>
+          <t>2015-01-24</t>
         </is>
       </c>
     </row>
@@ -1207,67 +1274,67 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F5" t="n">
         <v>26</v>
       </c>
       <c r="G5" t="n">
-        <v>0.422</v>
+        <v>0.409</v>
       </c>
       <c r="H5" t="n">
         <v>48.8</v>
       </c>
       <c r="I5" t="n">
-        <v>35.8</v>
+        <v>36.1</v>
       </c>
       <c r="J5" t="n">
-        <v>84.90000000000001</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.422</v>
+        <v>0.424</v>
       </c>
       <c r="L5" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="M5" t="n">
-        <v>18.5</v>
+        <v>18.7</v>
       </c>
       <c r="N5" t="n">
         <v>0.309</v>
       </c>
       <c r="O5" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="P5" t="n">
-        <v>23.8</v>
+        <v>23.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.73</v>
+        <v>0.733</v>
       </c>
       <c r="R5" t="n">
         <v>10.5</v>
       </c>
       <c r="S5" t="n">
-        <v>33.4</v>
+        <v>33.5</v>
       </c>
       <c r="T5" t="n">
         <v>43.9</v>
       </c>
       <c r="U5" t="n">
-        <v>19.9</v>
+        <v>20.2</v>
       </c>
       <c r="V5" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="W5" t="n">
         <v>5.7</v>
       </c>
       <c r="X5" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="n">
         <v>5.5</v>
@@ -1276,34 +1343,34 @@
         <v>18.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>94.8</v>
+        <v>95.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.6</v>
+        <v>-2.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AE5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AF5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AH5" t="n">
         <v>3</v>
       </c>
       <c r="AI5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK5" t="n">
         <v>29</v>
@@ -1318,25 +1385,25 @@
         <v>29</v>
       </c>
       <c r="AO5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP5" t="n">
         <v>14</v>
       </c>
-      <c r="AP5" t="n">
-        <v>12</v>
-      </c>
       <c r="AQ5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU5" t="n">
         <v>27</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>28</v>
       </c>
       <c r="AV5" t="n">
         <v>1</v>
@@ -1345,22 +1412,22 @@
         <v>30</v>
       </c>
       <c r="AX5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ5" t="n">
         <v>4</v>
       </c>
       <c r="BA5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB5" t="n">
         <v>26</v>
       </c>
       <c r="BC5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-24-2014-15</t>
+          <t>2015-01-24</t>
         </is>
       </c>
     </row>
@@ -1467,10 +1534,10 @@
         <v>2.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF6" t="n">
         <v>10</v>
@@ -1482,7 +1549,7 @@
         <v>15</v>
       </c>
       <c r="AI6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ6" t="n">
         <v>19</v>
@@ -1497,7 +1564,7 @@
         <v>16</v>
       </c>
       <c r="AN6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO6" t="n">
         <v>2</v>
@@ -1512,7 +1579,7 @@
         <v>6</v>
       </c>
       <c r="AS6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT6" t="n">
         <v>5</v>
@@ -1530,7 +1597,7 @@
         <v>1</v>
       </c>
       <c r="AY6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ6" t="n">
         <v>3</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-24-2014-15</t>
+          <t>2015-01-24</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>1.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE7" t="n">
         <v>13</v>
@@ -1664,7 +1731,7 @@
         <v>27</v>
       </c>
       <c r="AI7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ7" t="n">
         <v>21</v>
@@ -1685,10 +1752,10 @@
         <v>5</v>
       </c>
       <c r="AP7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR7" t="n">
         <v>12</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-24-2014-15</t>
+          <t>2015-01-24</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E8" t="n">
         <v>30</v>
       </c>
       <c r="F8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G8" t="n">
-        <v>0.698</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="H8" t="n">
         <v>48.6</v>
@@ -1771,7 +1838,7 @@
         <v>40.6</v>
       </c>
       <c r="J8" t="n">
-        <v>86.3</v>
+        <v>86.2</v>
       </c>
       <c r="K8" t="n">
         <v>0.471</v>
@@ -1780,34 +1847,34 @@
         <v>9.5</v>
       </c>
       <c r="M8" t="n">
-        <v>26.7</v>
+        <v>26.6</v>
       </c>
       <c r="N8" t="n">
-        <v>0.355</v>
+        <v>0.356</v>
       </c>
       <c r="O8" t="n">
         <v>17.3</v>
       </c>
       <c r="P8" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.763</v>
+        <v>0.765</v>
       </c>
       <c r="R8" t="n">
         <v>10.7</v>
       </c>
       <c r="S8" t="n">
-        <v>31.6</v>
+        <v>31.4</v>
       </c>
       <c r="T8" t="n">
-        <v>42.3</v>
+        <v>42.1</v>
       </c>
       <c r="U8" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="V8" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="W8" t="n">
         <v>8</v>
@@ -1825,31 +1892,31 @@
         <v>22.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>108.1</v>
+        <v>107.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="AE8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF8" t="n">
         <v>5</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>4</v>
       </c>
       <c r="AG8" t="n">
         <v>5</v>
       </c>
       <c r="AH8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AK8" t="n">
         <v>5</v>
@@ -1858,28 +1925,28 @@
         <v>7</v>
       </c>
       <c r="AM8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AN8" t="n">
         <v>12</v>
       </c>
       <c r="AO8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR8" t="n">
         <v>17</v>
       </c>
       <c r="AS8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT8" t="n">
         <v>20</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>19</v>
       </c>
       <c r="AU8" t="n">
         <v>7</v>
@@ -1891,10 +1958,10 @@
         <v>11</v>
       </c>
       <c r="AX8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ8" t="n">
         <v>15</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-24-2014-15</t>
+          <t>2015-01-24</t>
         </is>
       </c>
     </row>
@@ -2013,16 +2080,16 @@
         <v>-2.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AE9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF9" t="n">
         <v>18</v>
       </c>
       <c r="AG9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH9" t="n">
         <v>17</v>
@@ -2031,10 +2098,10 @@
         <v>13</v>
       </c>
       <c r="AJ9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL9" t="n">
         <v>14</v>
@@ -2064,10 +2131,10 @@
         <v>3</v>
       </c>
       <c r="AU9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW9" t="n">
         <v>24</v>
@@ -2076,7 +2143,7 @@
         <v>15</v>
       </c>
       <c r="AY9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AZ9" t="n">
         <v>30</v>
@@ -2088,7 +2155,7 @@
         <v>12</v>
       </c>
       <c r="BC9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-24-2014-15</t>
+          <t>2015-01-24</t>
         </is>
       </c>
     </row>
@@ -2117,28 +2184,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E10" t="n">
         <v>17</v>
       </c>
       <c r="F10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G10" t="n">
-        <v>0.386</v>
+        <v>0.395</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
       </c>
       <c r="I10" t="n">
-        <v>36.5</v>
+        <v>36.7</v>
       </c>
       <c r="J10" t="n">
         <v>86</v>
       </c>
       <c r="K10" t="n">
-        <v>0.425</v>
+        <v>0.426</v>
       </c>
       <c r="L10" t="n">
         <v>8.800000000000001</v>
@@ -2147,70 +2214,70 @@
         <v>25.3</v>
       </c>
       <c r="N10" t="n">
-        <v>0.346</v>
+        <v>0.349</v>
       </c>
       <c r="O10" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="P10" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="Q10" t="n">
         <v>0.699</v>
       </c>
       <c r="R10" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="S10" t="n">
-        <v>32.9</v>
+        <v>33</v>
       </c>
       <c r="T10" t="n">
         <v>45.8</v>
       </c>
       <c r="U10" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="V10" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="W10" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="X10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z10" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AA10" t="n">
         <v>19.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>97.90000000000001</v>
+        <v>98.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.9</v>
+        <v>-1.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AE10" t="n">
         <v>21</v>
       </c>
       <c r="AF10" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG10" t="n">
         <v>21</v>
       </c>
       <c r="AH10" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AI10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ10" t="n">
         <v>6</v>
@@ -2219,13 +2286,13 @@
         <v>28</v>
       </c>
       <c r="AL10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM10" t="n">
         <v>8</v>
       </c>
       <c r="AN10" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AO10" t="n">
         <v>25</v>
@@ -2246,7 +2313,7 @@
         <v>2</v>
       </c>
       <c r="AU10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AV10" t="n">
         <v>8</v>
@@ -2255,7 +2322,7 @@
         <v>12</v>
       </c>
       <c r="AX10" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AY10" t="n">
         <v>16</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-24-2014-15</t>
+          <t>2015-01-24</t>
         </is>
       </c>
     </row>
@@ -2404,13 +2471,13 @@
         <v>2</v>
       </c>
       <c r="AM11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN11" t="n">
         <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP11" t="n">
         <v>22</v>
@@ -2434,7 +2501,7 @@
         <v>25</v>
       </c>
       <c r="AW11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX11" t="n">
         <v>2</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-24-2014-15</t>
+          <t>2015-01-24</t>
         </is>
       </c>
     </row>
@@ -2481,61 +2548,61 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F12" t="n">
         <v>14</v>
       </c>
       <c r="G12" t="n">
-        <v>0.674</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="H12" t="n">
         <v>48.5</v>
       </c>
       <c r="I12" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J12" t="n">
-        <v>83.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.442</v>
+        <v>0.441</v>
       </c>
       <c r="L12" t="n">
         <v>11.8</v>
       </c>
       <c r="M12" t="n">
-        <v>33.4</v>
+        <v>33.3</v>
       </c>
       <c r="N12" t="n">
-        <v>0.353</v>
+        <v>0.354</v>
       </c>
       <c r="O12" t="n">
-        <v>17.6</v>
+        <v>17.9</v>
       </c>
       <c r="P12" t="n">
-        <v>24.4</v>
+        <v>25</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.718</v>
+        <v>0.717</v>
       </c>
       <c r="R12" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S12" t="n">
         <v>31.3</v>
       </c>
       <c r="T12" t="n">
-        <v>43.3</v>
+        <v>43.4</v>
       </c>
       <c r="U12" t="n">
         <v>21.2</v>
       </c>
       <c r="V12" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="W12" t="n">
         <v>9.800000000000001</v>
@@ -2547,37 +2614,37 @@
         <v>5.7</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.4</v>
+        <v>22.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>103</v>
+        <v>103.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>16</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>20</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>17</v>
       </c>
       <c r="AK12" t="n">
         <v>22</v>
@@ -2589,13 +2656,13 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AQ12" t="n">
         <v>28</v>
@@ -2607,10 +2674,10 @@
         <v>22</v>
       </c>
       <c r="AT12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV12" t="n">
         <v>29</v>
@@ -2619,19 +2686,19 @@
         <v>2</v>
       </c>
       <c r="AX12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AY12" t="n">
         <v>26</v>
       </c>
       <c r="AZ12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BB12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC12" t="n">
         <v>9</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-24-2014-15</t>
+          <t>2015-01-24</t>
         </is>
       </c>
     </row>
@@ -2741,10 +2808,10 @@
         <v>-2.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF13" t="n">
         <v>25</v>
@@ -2759,7 +2826,7 @@
         <v>27</v>
       </c>
       <c r="AJ13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK13" t="n">
         <v>27</v>
@@ -2780,7 +2847,7 @@
         <v>24</v>
       </c>
       <c r="AQ13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR13" t="n">
         <v>14</v>
@@ -2792,16 +2859,16 @@
         <v>6</v>
       </c>
       <c r="AU13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW13" t="n">
         <v>29</v>
       </c>
       <c r="AX13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY13" t="n">
         <v>18</v>
@@ -2810,7 +2877,7 @@
         <v>18</v>
       </c>
       <c r="BA13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB13" t="n">
         <v>27</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-24-2014-15</t>
+          <t>2015-01-24</t>
         </is>
       </c>
     </row>
@@ -2923,16 +2990,16 @@
         <v>7</v>
       </c>
       <c r="AD14" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AE14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH14" t="n">
         <v>26</v>
@@ -2947,10 +3014,10 @@
         <v>2</v>
       </c>
       <c r="AL14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM14" t="n">
         <v>4</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>5</v>
       </c>
       <c r="AN14" t="n">
         <v>3</v>
@@ -2968,7 +3035,7 @@
         <v>27</v>
       </c>
       <c r="AS14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT14" t="n">
         <v>26</v>
@@ -2992,7 +3059,7 @@
         <v>16</v>
       </c>
       <c r="BA14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB14" t="n">
         <v>4</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-24-2014-15</t>
+          <t>2015-01-24</t>
         </is>
       </c>
     </row>
@@ -3027,58 +3094,58 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E15" t="n">
         <v>12</v>
       </c>
       <c r="F15" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G15" t="n">
-        <v>0.279</v>
+        <v>0.273</v>
       </c>
       <c r="H15" t="n">
         <v>48.3</v>
       </c>
       <c r="I15" t="n">
-        <v>37.3</v>
+        <v>37.1</v>
       </c>
       <c r="J15" t="n">
-        <v>85.40000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="K15" t="n">
-        <v>0.437</v>
+        <v>0.435</v>
       </c>
       <c r="L15" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M15" t="n">
-        <v>19.7</v>
+        <v>19.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0.353</v>
+        <v>0.352</v>
       </c>
       <c r="O15" t="n">
-        <v>18.2</v>
+        <v>18.5</v>
       </c>
       <c r="P15" t="n">
-        <v>24.5</v>
+        <v>24.9</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.743</v>
+        <v>0.745</v>
       </c>
       <c r="R15" t="n">
         <v>11.4</v>
       </c>
       <c r="S15" t="n">
-        <v>31.7</v>
+        <v>31.5</v>
       </c>
       <c r="T15" t="n">
-        <v>43.1</v>
+        <v>42.9</v>
       </c>
       <c r="U15" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V15" t="n">
         <v>13</v>
@@ -3093,19 +3160,19 @@
         <v>4.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.9</v>
+        <v>20.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>99.8</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.5</v>
+        <v>-6.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3117,16 +3184,16 @@
         <v>27</v>
       </c>
       <c r="AH15" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AI15" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AJ15" t="n">
         <v>9</v>
       </c>
       <c r="AK15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL15" t="n">
         <v>21</v>
@@ -3135,10 +3202,10 @@
         <v>22</v>
       </c>
       <c r="AN15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP15" t="n">
         <v>7</v>
@@ -3150,22 +3217,22 @@
         <v>11</v>
       </c>
       <c r="AS15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT15" t="n">
         <v>15</v>
       </c>
       <c r="AU15" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AV15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW15" t="n">
         <v>18</v>
       </c>
       <c r="AX15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AY15" t="n">
         <v>9</v>
@@ -3174,10 +3241,10 @@
         <v>19</v>
       </c>
       <c r="BA15" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BB15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-24-2014-15</t>
+          <t>2015-01-24</t>
         </is>
       </c>
     </row>
@@ -3209,25 +3276,25 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E16" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F16" t="n">
         <v>12</v>
       </c>
       <c r="G16" t="n">
-        <v>0.721</v>
+        <v>0.714</v>
       </c>
       <c r="H16" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="I16" t="n">
         <v>38.8</v>
       </c>
       <c r="J16" t="n">
-        <v>83.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K16" t="n">
         <v>0.465</v>
@@ -3236,10 +3303,10 @@
         <v>5.5</v>
       </c>
       <c r="M16" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="N16" t="n">
-        <v>0.347</v>
+        <v>0.345</v>
       </c>
       <c r="O16" t="n">
         <v>18.4</v>
@@ -3248,46 +3315,46 @@
         <v>23.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.777</v>
+        <v>0.775</v>
       </c>
       <c r="R16" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="S16" t="n">
-        <v>32.5</v>
+        <v>32.3</v>
       </c>
       <c r="T16" t="n">
-        <v>42.8</v>
+        <v>42.7</v>
       </c>
       <c r="U16" t="n">
         <v>22.3</v>
       </c>
       <c r="V16" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="W16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="X16" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z16" t="n">
         <v>19.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB16" t="n">
         <v>101.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="AE16" t="n">
         <v>4</v>
@@ -3317,22 +3384,22 @@
         <v>27</v>
       </c>
       <c r="AN16" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AO16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AR16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT16" t="n">
         <v>16</v>
@@ -3341,28 +3408,28 @@
         <v>11</v>
       </c>
       <c r="AV16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX16" t="n">
         <v>22</v>
       </c>
       <c r="AY16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ16" t="n">
         <v>10</v>
       </c>
       <c r="BA16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB16" t="n">
         <v>14</v>
       </c>
       <c r="BC16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-24-2014-15</t>
+          <t>2015-01-24</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>-3.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AE17" t="n">
         <v>17</v>
@@ -3493,16 +3560,16 @@
         <v>10</v>
       </c>
       <c r="AL17" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AM17" t="n">
         <v>21</v>
       </c>
       <c r="AN17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP17" t="n">
         <v>11</v>
@@ -3520,7 +3587,7 @@
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AV17" t="n">
         <v>14</v>
@@ -3529,22 +3596,22 @@
         <v>8</v>
       </c>
       <c r="AX17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ17" t="n">
         <v>13</v>
       </c>
       <c r="BA17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-24-2014-15</t>
+          <t>2015-01-24</t>
         </is>
       </c>
     </row>
@@ -3573,100 +3640,100 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F18" t="n">
         <v>21</v>
       </c>
       <c r="G18" t="n">
-        <v>0.512</v>
+        <v>0.5</v>
       </c>
       <c r="H18" t="n">
         <v>48.6</v>
       </c>
       <c r="I18" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="J18" t="n">
         <v>81.3</v>
       </c>
       <c r="K18" t="n">
-        <v>0.463</v>
+        <v>0.462</v>
       </c>
       <c r="L18" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M18" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="N18" t="n">
-        <v>0.368</v>
+        <v>0.362</v>
       </c>
       <c r="O18" t="n">
-        <v>16.1</v>
+        <v>16.3</v>
       </c>
       <c r="P18" t="n">
-        <v>20.8</v>
+        <v>21.1</v>
       </c>
       <c r="Q18" t="n">
         <v>0.772</v>
       </c>
       <c r="R18" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="S18" t="n">
-        <v>30.8</v>
+        <v>30.7</v>
       </c>
       <c r="T18" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="U18" t="n">
-        <v>23.4</v>
+        <v>23.1</v>
       </c>
       <c r="V18" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="W18" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="X18" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z18" t="n">
         <v>22.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AB18" t="n">
-        <v>98.3</v>
+        <v>98.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="AD18" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE18" t="n">
         <v>16</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>14</v>
       </c>
       <c r="AF18" t="n">
         <v>14</v>
       </c>
       <c r="AG18" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AH18" t="n">
         <v>7</v>
       </c>
       <c r="AI18" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AJ18" t="n">
         <v>24</v>
@@ -3675,13 +3742,13 @@
         <v>8</v>
       </c>
       <c r="AL18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AM18" t="n">
         <v>25</v>
       </c>
       <c r="AN18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AO18" t="n">
         <v>24</v>
@@ -3690,16 +3757,16 @@
         <v>26</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS18" t="n">
         <v>24</v>
       </c>
       <c r="AT18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU18" t="n">
         <v>8</v>
@@ -3708,13 +3775,13 @@
         <v>28</v>
       </c>
       <c r="AW18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX18" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AY18" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AZ18" t="n">
         <v>28</v>
@@ -3726,7 +3793,7 @@
         <v>20</v>
       </c>
       <c r="BC18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-24-2014-15</t>
+          <t>2015-01-24</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-9.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE19" t="n">
         <v>30</v>
@@ -3848,7 +3915,7 @@
         <v>21</v>
       </c>
       <c r="AI19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ19" t="n">
         <v>8</v>
@@ -3869,7 +3936,7 @@
         <v>9</v>
       </c>
       <c r="AP19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ19" t="n">
         <v>21</v>
@@ -3893,7 +3960,7 @@
         <v>7</v>
       </c>
       <c r="AX19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY19" t="n">
         <v>27</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-24-2014-15</t>
+          <t>2015-01-24</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F20" t="n">
         <v>21</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5</v>
+        <v>0.512</v>
       </c>
       <c r="H20" t="n">
         <v>48.2</v>
@@ -3955,88 +4022,88 @@
         <v>38.3</v>
       </c>
       <c r="J20" t="n">
-        <v>83.59999999999999</v>
+        <v>84</v>
       </c>
       <c r="K20" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L20" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M20" t="n">
         <v>19</v>
       </c>
       <c r="N20" t="n">
-        <v>0.341</v>
+        <v>0.339</v>
       </c>
       <c r="O20" t="n">
         <v>17.1</v>
       </c>
       <c r="P20" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.762</v>
+        <v>0.753</v>
       </c>
       <c r="R20" t="n">
-        <v>11.5</v>
+        <v>11.8</v>
       </c>
       <c r="S20" t="n">
-        <v>31.9</v>
+        <v>32</v>
       </c>
       <c r="T20" t="n">
-        <v>43.4</v>
+        <v>43.9</v>
       </c>
       <c r="U20" t="n">
         <v>20.9</v>
       </c>
       <c r="V20" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="W20" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X20" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="Y20" t="n">
         <v>5.9</v>
       </c>
       <c r="Z20" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AB20" t="n">
         <v>100.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="AE20" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AF20" t="n">
         <v>14</v>
       </c>
       <c r="AG20" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI20" t="n">
         <v>10</v>
       </c>
       <c r="AJ20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK20" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AL20" t="n">
         <v>25</v>
@@ -4051,19 +4118,19 @@
         <v>18</v>
       </c>
       <c r="AP20" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AQ20" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AR20" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AS20" t="n">
         <v>17</v>
       </c>
       <c r="AT20" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AU20" t="n">
         <v>18</v>
@@ -4075,13 +4142,13 @@
         <v>23</v>
       </c>
       <c r="AX20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>29</v>
+      </c>
+      <c r="AZ20" t="n">
         <v>6</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>28</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>7</v>
       </c>
       <c r="BA20" t="n">
         <v>27</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-24-2014-15</t>
+          <t>2015-01-24</t>
         </is>
       </c>
     </row>
@@ -4119,85 +4186,85 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E21" t="n">
         <v>8</v>
       </c>
       <c r="F21" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G21" t="n">
-        <v>0.178</v>
+        <v>0.182</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
       </c>
       <c r="I21" t="n">
-        <v>35.9</v>
+        <v>36.1</v>
       </c>
       <c r="J21" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
       <c r="K21" t="n">
-        <v>0.439</v>
+        <v>0.441</v>
       </c>
       <c r="L21" t="n">
         <v>7.4</v>
       </c>
       <c r="M21" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="N21" t="n">
         <v>0.357</v>
       </c>
       <c r="O21" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="P21" t="n">
         <v>17.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.77</v>
+        <v>0.776</v>
       </c>
       <c r="R21" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="S21" t="n">
-        <v>29.2</v>
+        <v>28.9</v>
       </c>
       <c r="T21" t="n">
-        <v>39.8</v>
+        <v>39.5</v>
       </c>
       <c r="U21" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="V21" t="n">
         <v>14.8</v>
       </c>
       <c r="W21" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X21" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Y21" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="Z21" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="AA21" t="n">
         <v>18.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>92.8</v>
+        <v>93.3</v>
       </c>
       <c r="AC21" t="n">
         <v>-8</v>
       </c>
       <c r="AD21" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AE21" t="n">
         <v>28</v>
@@ -4209,10 +4276,10 @@
         <v>29</v>
       </c>
       <c r="AH21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ21" t="n">
         <v>23</v>
@@ -4236,10 +4303,10 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AR21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS21" t="n">
         <v>28</v>
@@ -4251,16 +4318,16 @@
         <v>14</v>
       </c>
       <c r="AV21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW21" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AX21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ21" t="n">
         <v>25</v>
@@ -4269,7 +4336,7 @@
         <v>28</v>
       </c>
       <c r="BB21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BC21" t="n">
         <v>28</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-24-2014-15</t>
+          <t>2015-01-24</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>1.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AE22" t="n">
         <v>14</v>
@@ -4394,10 +4461,10 @@
         <v>11</v>
       </c>
       <c r="AI22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK22" t="n">
         <v>21</v>
@@ -4415,7 +4482,7 @@
         <v>12</v>
       </c>
       <c r="AP22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ22" t="n">
         <v>23</v>
@@ -4439,13 +4506,13 @@
         <v>20</v>
       </c>
       <c r="AX22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY22" t="n">
         <v>10</v>
       </c>
       <c r="AZ22" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BA22" t="n">
         <v>17</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-24-2014-15</t>
+          <t>2015-01-24</t>
         </is>
       </c>
     </row>
@@ -4483,94 +4550,94 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E23" t="n">
         <v>15</v>
       </c>
       <c r="F23" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G23" t="n">
-        <v>0.333</v>
+        <v>0.326</v>
       </c>
       <c r="H23" t="n">
         <v>48.1</v>
       </c>
       <c r="I23" t="n">
-        <v>37.4</v>
+        <v>37.2</v>
       </c>
       <c r="J23" t="n">
         <v>81.8</v>
       </c>
       <c r="K23" t="n">
-        <v>0.457</v>
+        <v>0.455</v>
       </c>
       <c r="L23" t="n">
         <v>7.1</v>
       </c>
       <c r="M23" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="N23" t="n">
         <v>0.365</v>
       </c>
       <c r="O23" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="P23" t="n">
         <v>19.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.732</v>
+        <v>0.733</v>
       </c>
       <c r="R23" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>31.5</v>
+        <v>31.7</v>
       </c>
       <c r="T23" t="n">
-        <v>40.2</v>
+        <v>40.5</v>
       </c>
       <c r="U23" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V23" t="n">
         <v>14.7</v>
       </c>
       <c r="W23" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X23" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="Z23" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA23" t="n">
         <v>18.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>96</v>
+        <v>95.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.6</v>
+        <v>-5.9</v>
       </c>
       <c r="AD23" t="n">
         <v>1</v>
       </c>
       <c r="AE23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH23" t="n">
         <v>28</v>
@@ -4585,13 +4652,13 @@
         <v>13</v>
       </c>
       <c r="AL23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM23" t="n">
         <v>23</v>
       </c>
       <c r="AN23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO23" t="n">
         <v>29</v>
@@ -4600,13 +4667,13 @@
         <v>29</v>
       </c>
       <c r="AQ23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR23" t="n">
         <v>28</v>
       </c>
       <c r="AS23" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AT23" t="n">
         <v>28</v>
@@ -4615,7 +4682,7 @@
         <v>23</v>
       </c>
       <c r="AV23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW23" t="n">
         <v>15</v>
@@ -4624,7 +4691,7 @@
         <v>30</v>
       </c>
       <c r="AY23" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AZ23" t="n">
         <v>20</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-24-2014-15</t>
+          <t>2015-01-24</t>
         </is>
       </c>
     </row>
@@ -4665,28 +4732,28 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E24" t="n">
         <v>8</v>
       </c>
       <c r="F24" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G24" t="n">
-        <v>0.182</v>
+        <v>0.186</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
       </c>
       <c r="I24" t="n">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="J24" t="n">
         <v>81</v>
       </c>
       <c r="K24" t="n">
-        <v>0.408</v>
+        <v>0.409</v>
       </c>
       <c r="L24" t="n">
         <v>7.1</v>
@@ -4695,67 +4762,67 @@
         <v>23.9</v>
       </c>
       <c r="N24" t="n">
-        <v>0.299</v>
+        <v>0.297</v>
       </c>
       <c r="O24" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="P24" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.679</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="R24" t="n">
         <v>11.7</v>
       </c>
       <c r="S24" t="n">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="T24" t="n">
-        <v>41.9</v>
+        <v>41.8</v>
       </c>
       <c r="U24" t="n">
         <v>19.9</v>
       </c>
       <c r="V24" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="W24" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="X24" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Y24" t="n">
         <v>5.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA24" t="n">
         <v>20.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>89.8</v>
+        <v>90</v>
       </c>
       <c r="AC24" t="n">
-        <v>-12.5</v>
+        <v>-12.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
       </c>
       <c r="AF24" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG24" t="n">
         <v>28</v>
       </c>
       <c r="AH24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI24" t="n">
         <v>30</v>
@@ -4767,7 +4834,7 @@
         <v>30</v>
       </c>
       <c r="AL24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM24" t="n">
         <v>11</v>
@@ -4785,13 +4852,13 @@
         <v>30</v>
       </c>
       <c r="AR24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS24" t="n">
         <v>27</v>
       </c>
       <c r="AT24" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AU24" t="n">
         <v>29</v>
@@ -4806,13 +4873,13 @@
         <v>3</v>
       </c>
       <c r="AY24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-24-2014-15</t>
+          <t>2015-01-24</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>2.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="n">
         <v>12</v>
@@ -4943,7 +5010,7 @@
         <v>3</v>
       </c>
       <c r="AJ25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK25" t="n">
         <v>6</v>
@@ -4964,7 +5031,7 @@
         <v>23</v>
       </c>
       <c r="AQ25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR25" t="n">
         <v>16</v>
@@ -4985,13 +5052,13 @@
         <v>6</v>
       </c>
       <c r="AX25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA25" t="n">
         <v>13</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-24-2014-15</t>
+          <t>2015-01-24</t>
         </is>
       </c>
     </row>
@@ -5029,28 +5096,28 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E26" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F26" t="n">
         <v>13</v>
       </c>
       <c r="G26" t="n">
-        <v>0.711</v>
+        <v>0.705</v>
       </c>
       <c r="H26" t="n">
         <v>48.6</v>
       </c>
       <c r="I26" t="n">
-        <v>38.6</v>
+        <v>38.7</v>
       </c>
       <c r="J26" t="n">
         <v>86.59999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>0.445</v>
+        <v>0.446</v>
       </c>
       <c r="L26" t="n">
         <v>10.2</v>
@@ -5059,19 +5126,19 @@
         <v>27.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0.371</v>
+        <v>0.37</v>
       </c>
       <c r="O26" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="P26" t="n">
         <v>19.7</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.792</v>
+        <v>0.787</v>
       </c>
       <c r="R26" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="S26" t="n">
         <v>34.8</v>
@@ -5086,16 +5153,16 @@
         <v>13.8</v>
       </c>
       <c r="W26" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="X26" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y26" t="n">
         <v>3.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="AA26" t="n">
         <v>19.3</v>
@@ -5107,7 +5174,7 @@
         <v>5.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AE26" t="n">
         <v>3</v>
@@ -5119,7 +5186,7 @@
         <v>4</v>
       </c>
       <c r="AH26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI26" t="n">
         <v>8</v>
@@ -5131,13 +5198,13 @@
         <v>19</v>
       </c>
       <c r="AL26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM26" t="n">
         <v>2</v>
       </c>
       <c r="AN26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO26" t="n">
         <v>27</v>
@@ -5146,7 +5213,7 @@
         <v>28</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR26" t="n">
         <v>15</v>
@@ -5164,22 +5231,22 @@
         <v>9</v>
       </c>
       <c r="AW26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY26" t="n">
         <v>2</v>
       </c>
       <c r="AZ26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA26" t="n">
         <v>25</v>
       </c>
       <c r="BB26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC26" t="n">
         <v>5</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-24-2014-15</t>
+          <t>2015-01-24</t>
         </is>
       </c>
     </row>
@@ -5289,13 +5356,13 @@
         <v>-2.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AE27" t="n">
         <v>22</v>
       </c>
       <c r="AF27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG27" t="n">
         <v>22</v>
@@ -5310,7 +5377,7 @@
         <v>28</v>
       </c>
       <c r="AK27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL27" t="n">
         <v>29</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-24-2014-15</t>
+          <t>2015-01-24</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E28" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F28" t="n">
         <v>17</v>
       </c>
       <c r="G28" t="n">
-        <v>0.614</v>
+        <v>0.622</v>
       </c>
       <c r="H28" t="n">
         <v>49</v>
@@ -5411,49 +5478,49 @@
         <v>38.1</v>
       </c>
       <c r="J28" t="n">
-        <v>83.40000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.457</v>
+        <v>0.459</v>
       </c>
       <c r="L28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>22.1</v>
+        <v>22.3</v>
       </c>
       <c r="N28" t="n">
-        <v>0.369</v>
+        <v>0.372</v>
       </c>
       <c r="O28" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="P28" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="Q28" t="n">
         <v>0.764</v>
       </c>
       <c r="R28" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="S28" t="n">
-        <v>34</v>
+        <v>33.9</v>
       </c>
       <c r="T28" t="n">
-        <v>44</v>
+        <v>43.8</v>
       </c>
       <c r="U28" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="V28" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W28" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X28" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y28" t="n">
         <v>4.8</v>
@@ -5465,16 +5532,16 @@
         <v>20.1</v>
       </c>
       <c r="AB28" t="n">
-        <v>101.5</v>
+        <v>101.4</v>
       </c>
       <c r="AC28" t="n">
         <v>4</v>
       </c>
       <c r="AD28" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AE28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF28" t="n">
         <v>11</v>
@@ -5489,10 +5556,10 @@
         <v>11</v>
       </c>
       <c r="AJ28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AL28" t="n">
         <v>11</v>
@@ -5501,16 +5568,16 @@
         <v>15</v>
       </c>
       <c r="AN28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP28" t="n">
         <v>20</v>
       </c>
       <c r="AQ28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR28" t="n">
         <v>25</v>
@@ -5519,7 +5586,7 @@
         <v>5</v>
       </c>
       <c r="AT28" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AU28" t="n">
         <v>6</v>
@@ -5540,13 +5607,13 @@
         <v>9</v>
       </c>
       <c r="BA28" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BB28" t="n">
         <v>15</v>
       </c>
       <c r="BC28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-24-2014-15</t>
+          <t>2015-01-24</t>
         </is>
       </c>
     </row>
@@ -5653,13 +5720,13 @@
         <v>5</v>
       </c>
       <c r="AD29" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AE29" t="n">
         <v>10</v>
       </c>
       <c r="AF29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG29" t="n">
         <v>9</v>
@@ -5677,7 +5744,7 @@
         <v>14</v>
       </c>
       <c r="AL29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM29" t="n">
         <v>7</v>
@@ -5701,7 +5768,7 @@
         <v>26</v>
       </c>
       <c r="AT29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU29" t="n">
         <v>19</v>
@@ -5713,7 +5780,7 @@
         <v>17</v>
       </c>
       <c r="AX29" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AY29" t="n">
         <v>19</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-24-2014-15</t>
+          <t>2015-01-24</t>
         </is>
       </c>
     </row>
@@ -5757,88 +5824,88 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F30" t="n">
         <v>28</v>
       </c>
       <c r="G30" t="n">
-        <v>0.364</v>
+        <v>0.349</v>
       </c>
       <c r="H30" t="n">
         <v>48</v>
       </c>
       <c r="I30" t="n">
-        <v>35.6</v>
+        <v>35.5</v>
       </c>
       <c r="J30" t="n">
         <v>78.90000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>0.452</v>
+        <v>0.45</v>
       </c>
       <c r="L30" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M30" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="N30" t="n">
-        <v>0.343</v>
+        <v>0.339</v>
       </c>
       <c r="O30" t="n">
-        <v>17.3</v>
+        <v>17.5</v>
       </c>
       <c r="P30" t="n">
-        <v>23</v>
+        <v>23.2</v>
       </c>
       <c r="Q30" t="n">
         <v>0.753</v>
       </c>
       <c r="R30" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S30" t="n">
-        <v>31</v>
+        <v>30.8</v>
       </c>
       <c r="T30" t="n">
-        <v>42.5</v>
+        <v>42.4</v>
       </c>
       <c r="U30" t="n">
         <v>20.4</v>
       </c>
       <c r="V30" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="W30" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="X30" t="n">
         <v>5.8</v>
       </c>
       <c r="Y30" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z30" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AB30" t="n">
-        <v>95.8</v>
+        <v>95.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>-2.7</v>
+        <v>-3.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AE30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF30" t="n">
         <v>24</v>
@@ -5859,16 +5926,16 @@
         <v>17</v>
       </c>
       <c r="AL30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AM30" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AN30" t="n">
         <v>20</v>
       </c>
       <c r="AO30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP30" t="n">
         <v>15</v>
@@ -5877,7 +5944,7 @@
         <v>17</v>
       </c>
       <c r="AR30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS30" t="n">
         <v>23</v>
@@ -5892,13 +5959,13 @@
         <v>26</v>
       </c>
       <c r="AW30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX30" t="n">
         <v>5</v>
       </c>
       <c r="AY30" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ30" t="n">
         <v>5</v>
@@ -5910,7 +5977,7 @@
         <v>24</v>
       </c>
       <c r="BC30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-24-2014-15</t>
+          <t>2015-01-24</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E31" t="n">
         <v>29</v>
       </c>
       <c r="F31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G31" t="n">
-        <v>0.659</v>
+        <v>0.674</v>
       </c>
       <c r="H31" t="n">
         <v>48.5</v>
@@ -5969,22 +6036,22 @@
         <v>15.8</v>
       </c>
       <c r="N31" t="n">
-        <v>0.381</v>
+        <v>0.382</v>
       </c>
       <c r="O31" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="P31" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="Q31" t="n">
         <v>0.74</v>
       </c>
       <c r="R31" t="n">
-        <v>10.3</v>
+        <v>10.5</v>
       </c>
       <c r="S31" t="n">
-        <v>33.2</v>
+        <v>33</v>
       </c>
       <c r="T31" t="n">
         <v>43.5</v>
@@ -6002,34 +6069,34 @@
         <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Z31" t="n">
         <v>21</v>
       </c>
       <c r="AA31" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>99.5</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AE31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF31" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AG31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH31" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AI31" t="n">
         <v>6</v>
@@ -6059,19 +6126,19 @@
         <v>24</v>
       </c>
       <c r="AR31" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AS31" t="n">
         <v>10</v>
       </c>
       <c r="AT31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU31" t="n">
         <v>5</v>
       </c>
       <c r="AV31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW31" t="n">
         <v>14</v>
@@ -6086,10 +6153,10 @@
         <v>17</v>
       </c>
       <c r="BA31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC31" t="n">
         <v>12</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-24-2014-15</t>
+          <t>2015-01-24</t>
         </is>
       </c>
     </row>
